--- a/Task 2 Sales Profit &Customer Metrics/Sales Profit & Customer Metrics.xlsx
+++ b/Task 2 Sales Profit &Customer Metrics/Sales Profit & Customer Metrics.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alpha\OneDrive\Documents\My Coding Samurai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ajibola Modupe\Desktop\codding-samurai\Task 2 Sales Profit &amp;Customer Metrics\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EB300D-8F30-4598-83B0-A034FEE206F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10305" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot table" sheetId="2" r:id="rId1"/>
@@ -21,9 +22,9 @@
     <definedName name="Slicer_Month">#N/A</definedName>
     <definedName name="Slicer_Quarter">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -45,8 +46,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -248,12 +247,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.0,&quot;k&quot;"/>
-    <numFmt numFmtId="165" formatCode="0.0,&quot;K&quot;"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0,&quot;k&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0,&quot;K&quot;"/>
     <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5">
@@ -334,13 +333,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -348,8 +347,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
@@ -363,6 +362,36 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0,&quot;k&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="0.0,&quot;K&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0.0,&quot;k&quot;"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -396,27 +425,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="0.0,&quot;K&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0,&quot;k&quot;"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0,&quot;k&quot;"/>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -457,29 +465,20 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="4">
-      <tableStyleElement type="wholeTable" dxfId="12"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
     </tableStyle>
-    <tableStyle name="Slicer Style 2" pivot="0" table="0" count="6">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
+    <tableStyle name="Slicer Style 2" pivot="0" table="0" count="6" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="wholeTable" dxfId="13"/>
+      <tableStyleElement type="headerRow" dxfId="12"/>
     </tableStyle>
-    <tableStyle name="Slicer Style 3" pivot="0" table="0" count="0"/>
-    <tableStyle name="SlicerStyleOther1 2" pivot="0" table="0" count="10">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+    <tableStyle name="Slicer Style 3" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}"/>
+    <tableStyle name="SlicerStyleOther1 2" pivot="0" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="wholeTable" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -720,6 +719,36 @@
         <dxf>
           <fill>
             <patternFill>
+              <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+            </patternFill>
+          </fill>
+          <border diagonalUp="0" diagonalDown="0">
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill>
+              <bgColor theme="1"/>
+            </patternFill>
+          </fill>
+          <border diagonalUp="0" diagonalDown="0">
+            <left/>
+            <right/>
+            <top/>
+            <bottom/>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <fill>
+            <patternFill>
               <bgColor theme="2"/>
             </patternFill>
           </fill>
@@ -736,36 +765,6 @@
           <fill>
             <patternFill>
               <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-            </patternFill>
-          </fill>
-          <border diagonalUp="0" diagonalDown="0">
-            <left/>
-            <right/>
-            <top/>
-            <bottom/>
-            <vertical/>
-            <horizontal/>
-          </border>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill>
-              <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-            </patternFill>
-          </fill>
-          <border diagonalUp="0" diagonalDown="0">
-            <left/>
-            <right/>
-            <top/>
-            <bottom/>
-            <vertical/>
-            <horizontal/>
-          </border>
-        </dxf>
-        <dxf>
-          <fill>
-            <patternFill>
-              <bgColor theme="1"/>
             </patternFill>
           </fill>
           <border diagonalUp="0" diagonalDown="0">
@@ -806,10 +805,10 @@
         </x14:slicerStyle>
         <x14:slicerStyle name="Slicer Style 2">
           <x14:slicerStyleElements>
-            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="9"/>
-            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="8"/>
-            <x14:slicerStyleElement type="selectedItemWithData" dxfId="11"/>
-            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="10"/>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="11"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="10"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="9"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="8"/>
           </x14:slicerStyleElements>
         </x14:slicerStyle>
         <x14:slicerStyle name="Slicer Style 3"/>
@@ -835,7 +834,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -915,7 +914,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -973,7 +972,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -988,7 +986,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1000,7 +998,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
@@ -1010,9 +1008,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -1069,7 +1065,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -1081,7 +1077,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1093,7 +1089,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1166,6 +1161,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-41CD-418F-8389-6E8C52CB073E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1220,7 +1220,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-552403040"/>
@@ -1265,7 +1265,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-552386176"/>
@@ -1299,7 +1299,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1320,7 +1320,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1406,7 +1406,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1458,7 +1458,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1473,7 +1472,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -1485,7 +1484,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="outEnd"/>
@@ -1496,9 +1495,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -1558,7 +1555,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -1570,7 +1567,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1583,7 +1580,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1643,6 +1639,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5F28-413C-8330-12AA8F648955}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1652,7 +1653,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
+        <c:gapWidth val="42"/>
         <c:axId val="-2042813264"/>
         <c:axId val="-2042812176"/>
       </c:barChart>
@@ -1697,7 +1698,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-2042812176"/>
@@ -1742,7 +1743,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-2042813264"/>
@@ -1780,7 +1781,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1801,7 +1802,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -1887,7 +1888,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1940,6 +1941,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
@@ -2002,7 +2044,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2027,7 +2068,7 @@
                   <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="ctr"/>
@@ -2038,9 +2079,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2141,6 +2180,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E347-404F-AA34-1842E3ACD590}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2196,7 +2240,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-2042821424"/>
@@ -2241,7 +2285,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-2042831760"/>
@@ -2289,7 +2333,7 @@
           <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2310,7 +2354,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2363,7 +2407,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2389,7 +2432,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2471,7 +2514,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2480,13 +2522,13 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="bg1"/>
                   </a:solidFill>
@@ -2495,7 +2537,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="ctr"/>
@@ -2506,9 +2548,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2530,7 +2570,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -2545,7 +2584,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="75000"/>
@@ -2557,7 +2596,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="ctr"/>
@@ -2568,9 +2607,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2624,13 +2661,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="bg1"/>
                     </a:solidFill>
@@ -2639,7 +2676,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -2652,7 +2689,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -2724,6 +2760,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2608-4BDE-BA2D-67A281EC1ECB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2766,7 +2807,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -2778,7 +2819,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -2791,7 +2832,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -2863,6 +2903,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2608-4BDE-BA2D-67A281EC1ECB}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="ctr"/>
@@ -2873,7 +2918,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="146"/>
+        <c:gapWidth val="42"/>
         <c:overlap val="100"/>
         <c:axId val="-1922558304"/>
         <c:axId val="-1922545792"/>
@@ -2919,7 +2964,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-1922545792"/>
@@ -2964,7 +3009,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-1922558304"/>
@@ -2998,7 +3043,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3019,7 +3064,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3105,7 +3150,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3157,7 +3202,6 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -3172,17 +3216,14 @@
               <a:pPr>
                 <a:defRPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
                   <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:dLblPos val="ctr"/>
@@ -3193,9 +3234,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -3255,17 +3294,14 @@
                 <a:pPr>
                   <a:defRPr lang="en-GB" sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
                     <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="ctr"/>
@@ -3278,7 +3314,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -3350,6 +3385,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-30F9-47E5-936B-60168F5D9447}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="ctr"/>
@@ -3360,8 +3400,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="42"/>
+        <c:overlap val="-25"/>
         <c:axId val="-1922538176"/>
         <c:axId val="-1922552864"/>
       </c:barChart>
@@ -3406,7 +3446,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-1922552864"/>
@@ -3451,7 +3491,7 @@
                 <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-NG"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="-1922538176"/>
@@ -3495,7 +3535,7 @@
           <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3516,7 +3556,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -3602,7 +3642,7 @@
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-NG"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3690,33 +3730,25 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
-            <a:solidFill>
-              <a:sysClr val="window" lastClr="FFFFFF"/>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="25000"/>
-                  <a:lumOff val="75000"/>
-                </a:sysClr>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
                     </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
@@ -3724,28 +3756,17 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                <a:prstGeom prst="wedgeRectCallout">
-                  <a:avLst/>
-                </a:prstGeom>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-              </c15:spPr>
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -3766,11 +3787,14 @@
         </c:spPr>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="0.22150750683708209"/>
+              <c:y val="0.24538282380326423"/>
+            </c:manualLayout>
+          </c:layout>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -3783,30 +3807,33 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="930" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="1"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
               <c15:layout>
                 <c:manualLayout>
-                  <c:w val="9.7055032330768468E-2"/>
-                  <c:h val="0.12749642638026609"/>
+                  <c:w val="0.14205235975986183"/>
+                  <c:h val="0.15658740934464851"/>
                 </c:manualLayout>
               </c15:layout>
             </c:ext>
@@ -3828,6 +3855,60 @@
           </a:ln>
           <a:effectLst/>
         </c:spPr>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout>
+            <c:manualLayout>
+              <c:x val="-0.23595779550776855"/>
+              <c:y val="-0.23290557565206685"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-NG"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout>
+                <c:manualLayout>
+                  <c:w val="0.17907211410531196"/>
+                  <c:h val="0.11639056614524898"/>
+                </c:manualLayout>
+              </c15:layout>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -3836,8 +3917,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.18929872214046672"/>
-          <c:y val="0.23760857453352896"/>
+          <c:x val="0.24895115467476345"/>
+          <c:y val="0.24176758040842308"/>
           <c:w val="0.59770543615872651"/>
           <c:h val="0.60965968497667056"/>
         </c:manualLayout>
@@ -3865,7 +3946,6 @@
               </a:schemeClr>
             </a:solidFill>
           </c:spPr>
-          <c:explosion val="6"/>
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
@@ -3882,6 +3962,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-538E-4EDF-A40C-344168EEBE90}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -3899,15 +3984,23 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-538E-4EDF-A40C-344168EEBE90}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
-              <c:layout/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.22150750683708209"/>
+                  <c:y val="0.24538282380326423"/>
+                </c:manualLayout>
+              </c:layout>
               <c:spPr>
-                <a:solidFill>
-                  <a:schemeClr val="bg1"/>
-                </a:solidFill>
+                <a:noFill/>
                 <a:ln>
                   <a:noFill/>
                 </a:ln>
@@ -3920,61 +4013,117 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="930" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1"/>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
                       </a:solidFill>
                       <a:latin typeface="+mn-lt"/>
                       <a:ea typeface="+mn-ea"/>
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="en-NG"/>
                 </a:p>
               </c:txPr>
               <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="1"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
               <c:showSerName val="0"/>
-              <c:showPercent val="1"/>
+              <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="9.7055032330768468E-2"/>
-                      <c:h val="0.12749642638026609"/>
+                      <c:w val="0.14205235975986183"/>
+                      <c:h val="0.15658740934464851"/>
                     </c:manualLayout>
                   </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-538E-4EDF-A40C-344168EEBE90}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.23595779550776855"/>
+                  <c:y val="-0.23290557565206685"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:noAutofit/>
+                </a:bodyPr>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="75000"/>
+                          <a:lumOff val="25000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-NG"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.17907211410531196"/>
+                      <c:h val="0.11639056614524898"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-538E-4EDF-A40C-344168EEBE90}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:spPr>
-              <a:solidFill>
-                <a:sysClr val="window" lastClr="FFFFFF"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:ln>
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="25000"/>
-                    <a:lumOff val="75000"/>
-                  </a:sysClr>
-                </a:solidFill>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
                       </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
@@ -3982,29 +4131,32 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-NG"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="1"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="1"/>
+            <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <a:prstGeom prst="wedgeRectCallout">
-                    <a:avLst/>
-                  </a:prstGeom>
-                  <a:noFill/>
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
-                </c15:spPr>
-                <c15:layout/>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
           <c:cat>
@@ -4036,6 +4188,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-538E-4EDF-A40C-344168EEBE90}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -4044,7 +4201,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
         <c:holeSize val="50"/>
@@ -4078,7 +4235,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-NG"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -7396,25 +7553,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>107022</xdr:colOff>
+      <xdr:colOff>143912</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>21405</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>88079</xdr:rowOff>
+      <xdr:colOff>58295</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>72571</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rounded Rectangle 1"/>
+        <xdr:cNvPr id="2" name="Rounded Rectangle 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="107022" y="0"/>
-          <a:ext cx="18407866" cy="9548866"/>
+          <a:off x="143912" y="0"/>
+          <a:ext cx="18088083" cy="8962571"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7472,7 +7635,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rounded Rectangle 5"/>
+        <xdr:cNvPr id="6" name="Rounded Rectangle 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7536,7 +7705,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Rounded Rectangle 6"/>
+        <xdr:cNvPr id="7" name="Rounded Rectangle 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7600,7 +7775,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Rounded Rectangle 7"/>
+        <xdr:cNvPr id="8" name="Rounded Rectangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7664,7 +7845,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Rounded Rectangle 8"/>
+        <xdr:cNvPr id="9" name="Rounded Rectangle 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7728,7 +7915,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Rounded Rectangle 9"/>
+        <xdr:cNvPr id="10" name="Rounded Rectangle 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7792,7 +7985,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Rounded Rectangle 10"/>
+        <xdr:cNvPr id="11" name="Rounded Rectangle 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7856,7 +8055,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Rounded Rectangle 11"/>
+        <xdr:cNvPr id="12" name="Rounded Rectangle 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7920,7 +8125,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Rounded Rectangle 12"/>
+        <xdr:cNvPr id="13" name="Rounded Rectangle 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7984,7 +8195,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Rounded Rectangle 13"/>
+        <xdr:cNvPr id="14" name="Rounded Rectangle 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8048,7 +8265,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="Rounded Rectangle 15"/>
+        <xdr:cNvPr id="16" name="Rounded Rectangle 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8112,7 +8335,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="18" name="Picture 17"/>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8150,7 +8379,13 @@
     </xdr:to>
     <xdr:pic macro="[0]!Picture19_Click">
       <xdr:nvPicPr>
-        <xdr:cNvPr id="20" name="Picture 19"/>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8190,7 +8425,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="TextBox 20"/>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8250,7 +8491,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!C28">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="TextBox 21"/>
+        <xdr:cNvPr id="22" name="TextBox 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000016000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8291,6 +8538,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t> $68,495 </a:t>
           </a:fld>
           <a:endParaRPr lang="en-GB" sz="2400"/>
@@ -8314,7 +8562,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A28">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="TextBox 22"/>
+        <xdr:cNvPr id="23" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8357,6 +8611,7 @@
               <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>Sales</a:t>
           </a:fld>
           <a:endParaRPr lang="en-GB" sz="2400" b="1">
@@ -8384,7 +8639,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A30">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="TextBox 25"/>
+        <xdr:cNvPr id="26" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8447,25 +8708,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>630466</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>134419</xdr:rowOff>
+      <xdr:colOff>91204</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>5464</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>563794</xdr:colOff>
+      <xdr:colOff>24532</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>96320</xdr:rowOff>
+      <xdr:rowOff>143212</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!C30">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="TextBox 26"/>
+        <xdr:cNvPr id="27" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17069118" y="1771863"/>
-          <a:ext cx="1303215" cy="507715"/>
+          <a:off x="16128373" y="1763926"/>
+          <a:ext cx="1269759" cy="489440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8534,7 +8801,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="Picture 30"/>
+        <xdr:cNvPr id="31" name="Picture 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8574,7 +8847,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Picture 31"/>
+        <xdr:cNvPr id="32" name="Picture 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8612,7 +8891,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Picture 32"/>
+        <xdr:cNvPr id="33" name="Picture 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8650,7 +8935,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Picture 33"/>
+        <xdr:cNvPr id="34" name="Picture 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8688,7 +8979,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="35" name="Chart 34"/>
+        <xdr:cNvPr id="35" name="Chart 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -8720,7 +9017,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="36" name="Chart 35"/>
+        <xdr:cNvPr id="36" name="Chart 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -8752,7 +9055,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="Rounded Rectangle 41"/>
+        <xdr:cNvPr id="42" name="Rounded Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8816,7 +9125,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="43" name="Chart 42"/>
+        <xdr:cNvPr id="43" name="Chart 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -8846,11 +9161,17 @@
       <xdr:row>40</xdr:row>
       <xdr:rowOff>64215</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="45" name="Month"/>
+            <xdr:cNvPr id="45" name="Month">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002D000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -8864,7 +9185,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8918,11 +9239,17 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>42809</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="46" name="Quarter"/>
+            <xdr:cNvPr id="46" name="Quarter">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002E000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvGraphicFramePr/>
           </xdr:nvGraphicFramePr>
           <xdr:xfrm>
@@ -8936,7 +9263,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -8992,7 +9319,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="TextBox 46"/>
+        <xdr:cNvPr id="47" name="TextBox 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9047,7 +9380,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="Rounded Rectangle 52"/>
+        <xdr:cNvPr id="53" name="Rounded Rectangle 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9111,7 +9450,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!C29">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="TextBox 53"/>
+        <xdr:cNvPr id="54" name="TextBox 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9186,7 +9531,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A29">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="TextBox 54"/>
+        <xdr:cNvPr id="55" name="TextBox 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9261,7 +9612,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!C31">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="TextBox 55"/>
+        <xdr:cNvPr id="56" name="TextBox 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9336,7 +9693,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A31">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="TextBox 56"/>
+        <xdr:cNvPr id="57" name="TextBox 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9411,7 +9774,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="58" name="Rounded Rectangle 57"/>
+        <xdr:cNvPr id="58" name="Rounded Rectangle 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9475,7 +9844,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A51">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="TextBox 58"/>
+        <xdr:cNvPr id="59" name="TextBox 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9538,25 +9913,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>577918</xdr:colOff>
+      <xdr:colOff>413795</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>171236</xdr:rowOff>
+      <xdr:rowOff>7113</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>245399</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>132172</xdr:rowOff>
+      <xdr:colOff>81276</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>143895</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!D51">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="TextBox 60"/>
+        <xdr:cNvPr id="61" name="TextBox 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13591851" y="1990618"/>
-          <a:ext cx="2407256" cy="506751"/>
+          <a:off x="13109887" y="1765575"/>
+          <a:ext cx="2340343" cy="488474"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9625,7 +10006,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!D50">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="TextBox 61"/>
+        <xdr:cNvPr id="62" name="TextBox 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9688,25 +10075,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>652837</xdr:colOff>
+      <xdr:colOff>652838</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>149833</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>320317</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>351035</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>110769</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="'Pivot table'!A50">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="TextBox 62"/>
+        <xdr:cNvPr id="63" name="TextBox 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10926994" y="1423400"/>
-          <a:ext cx="2407256" cy="506751"/>
+          <a:off x="10670141" y="1348485"/>
+          <a:ext cx="1701658" cy="474644"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9775,7 +10168,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="Rounded Rectangle 63"/>
+        <xdr:cNvPr id="64" name="Rounded Rectangle 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -9827,25 +10226,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>470899</xdr:colOff>
+      <xdr:colOff>506068</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>107025</xdr:rowOff>
+      <xdr:rowOff>130472</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>476036</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>160535</xdr:rowOff>
+      <xdr:colOff>511205</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>8136</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="65" name="Rounded Rectangle 64"/>
+        <xdr:cNvPr id="65" name="Rounded Rectangle 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10060112" y="5747109"/>
-          <a:ext cx="4114800" cy="3328398"/>
+          <a:off x="9861083" y="5581703"/>
+          <a:ext cx="4014430" cy="3218741"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -9903,7 +10308,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="67" name="Chart 66"/>
+        <xdr:cNvPr id="67" name="Chart 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -9935,7 +10346,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="68" name="Chart 67"/>
+        <xdr:cNvPr id="68" name="Chart 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -9955,19 +10372,25 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>171239</xdr:colOff>
+      <xdr:colOff>70338</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>107022</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>651770</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>164123</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>171235</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="70" name="Chart 69"/>
+        <xdr:cNvPr id="70" name="Chart 69">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000046000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -9999,7 +10422,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="71" name="Rounded Rectangle 70"/>
+        <xdr:cNvPr id="71" name="Rounded Rectangle 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10063,7 +10492,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="TextBox 47"/>
+        <xdr:cNvPr id="48" name="TextBox 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -10074,15 +10509,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
+          <a:noFill/>
         </a:ln>
       </xdr:spPr>
       <xdr:style>
@@ -10192,10 +10621,6 @@
           <a:br>
             <a:rPr lang="en-GB" sz="1400" b="1"/>
           </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1400"/>
-            <a:t/>
-          </a:r>
           <a:br>
             <a:rPr lang="en-GB" sz="1400"/>
           </a:br>
@@ -10274,11 +10699,131 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>650697</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>111303</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>342472</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>119865</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Arrow: Up 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC384786-FCD8-44C2-88AF-BC246B474310}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10000180" y="1481191"/>
+          <a:ext cx="359595" cy="351034"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>145550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>325349</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>136988</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Arrow: Down 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{625175A5-916A-4674-9082-31E14E146236}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12688585" y="1515438"/>
+          <a:ext cx="325348" cy="333910"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="dk1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-NG" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Alpha Bamidele" refreshedDate="45905.237379398146" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="63">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Alpha Bamidele" refreshedDate="45905.237379398146" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="63" xr:uid="{00000000-000A-0000-FFFF-FFFF11000000}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -10358,7 +10903,7 @@
         <s v="North"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Sales" numFmtId="43">
+    <cacheField name="Sales" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1000" maxValue="6500" count="28">
         <n v="2581"/>
         <n v="3944"/>
@@ -10390,10 +10935,10 @@
         <n v="2450"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Profit" numFmtId="43">
+    <cacheField name="Profit" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="385.71428571428601" maxValue="5214.2857142857101"/>
     </cacheField>
-    <cacheField name="Target Sales" numFmtId="43">
+    <cacheField name="Target Sales" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="285.71428571428572" maxValue="6714.2857142857101"/>
     </cacheField>
     <cacheField name="No of Customers" numFmtId="0">
@@ -11530,11 +12075,107 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
-  <location ref="G34:H37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000009000000}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C34:D41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-00000A000000}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="E34:F39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="0"/>
         <item x="3"/>
@@ -11543,7 +12184,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="43" showAll="0">
+    <pivotField dataField="1" numFmtId="165" showAll="0">
       <items count="29">
         <item x="11"/>
         <item x="14"/>
@@ -11576,174 +12217,14 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="4">
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="12" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable16" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="N3:O9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="13">
@@ -11773,9 +12254,9 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="9"/>
+    <field x="1"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
@@ -11788,9 +12269,6 @@
     <i>
       <x v="3"/>
     </i>
-    <i>
-      <x v="4"/>
-    </i>
     <i t="grand">
       <x/>
     </i>
@@ -11801,151 +12279,31 @@
   <dataFields count="1">
     <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="6">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+  <chartFormats count="1">
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="9" count="0"/>
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
         </references>
       </pivotArea>
-    </format>
-  </formats>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable15" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="K3:L9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Score" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable48" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000008000000}" name="PivotTable48" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
@@ -11968,9 +12326,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12038,7 +12396,7 @@
     <dataField name="Sum of No of Customers" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="2">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="12" count="0"/>
@@ -12062,12 +12420,211 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000006000000}" name="PivotTable44" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A21:A22" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="24">
+        <item x="17"/>
+        <item x="4"/>
+        <item x="22"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="14"/>
+        <item x="9"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="20"/>
+        <item x="19"/>
+        <item x="10"/>
+        <item x="0"/>
+        <item x="11"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="21"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="15"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Profit Completion Rate" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="9">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable39" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000002000000}" name="PivotTable42" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Customer Completion Rate" fld="8" subtotal="average" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable39" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A11:A12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
@@ -12090,9 +12647,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
       <items count="30">
@@ -12174,12 +12731,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable40" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000001000000}" name="PivotTable40" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B11:B12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
@@ -12202,9 +12762,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
@@ -12280,13 +12840,16 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable42" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C11:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="PivotTable13" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
       <items count="15">
@@ -12308,13 +12871,207 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
+    <dataField name=" Target Sales" fld="4" baseField="12" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="12" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000005000000}" name="PivotTable43" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A19:A20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="30">
+        <item x="7"/>
+        <item x="16"/>
+        <item x="25"/>
+        <item x="21"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="26"/>
+        <item x="24"/>
+        <item x="28"/>
+        <item x="3"/>
+        <item x="15"/>
+        <item x="18"/>
+        <item x="2"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="13"/>
+        <item x="20"/>
+        <item x="0"/>
+        <item x="10"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="4"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12352,241 +13109,27 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Customer Completion Rate" fld="8" subtotal="average" baseField="0" baseItem="0"/>
+    <dataField name="Average of Sales Completion Rate" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
   </dataFields>
+  <formats count="1">
+    <format dxfId="4">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable6" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="E34:F39" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="43" showAll="0">
-      <items count="29">
-        <item x="11"/>
-        <item x="14"/>
-        <item x="24"/>
-        <item x="8"/>
-        <item x="18"/>
-        <item x="17"/>
-        <item x="23"/>
-        <item x="7"/>
-        <item x="3"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="5"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="6"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="C34:D41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A34:B41" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
@@ -12609,9 +13152,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12718,12 +13261,152 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable45" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000004000000}" name="PivotTable16" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="N3:O9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="9" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000007000000}" name="PivotTable45" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A23:A24" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
@@ -12746,9 +13429,9 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12793,7 +13476,7 @@
     <dataField name="Average of Customer Completion Rate" fld="8" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -12802,12 +13485,143 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable14" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000003000000}" name="PivotTable15" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K3:L9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Score" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="PivotTable14" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G3:I8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField numFmtId="14" showAll="0">
@@ -12838,9 +13652,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -12924,341 +13738,64 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable44" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A21:A22" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="24">
-        <item x="17"/>
-        <item x="4"/>
-        <item x="22"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="14"/>
-        <item x="9"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="10"/>
-        <item x="0"/>
-        <item x="11"/>
-        <item x="7"/>
-        <item x="12"/>
-        <item x="21"/>
-        <item x="13"/>
-        <item x="1"/>
-        <item x="15"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of Profit Completion Rate" fld="7" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="4">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable13" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item h="1" x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
-    <dataField name=" Target Sales" fld="4" baseField="12" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="8">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="12" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="4">
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable43" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A19:A20" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-00000B000000}" name="PivotTable9" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+  <location ref="G34:H37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
-    <pivotField numFmtId="14" showAll="0">
-      <items count="15">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
         <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
         <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="165" showAll="0">
+      <items count="29">
+        <item x="11"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="18"/>
+        <item x="17"/>
+        <item x="23"/>
+        <item x="7"/>
+        <item x="3"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="5"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="6"/>
+        <item x="27"/>
+        <item x="19"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="9"/>
         <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
+        <item x="1"/>
         <item x="10"/>
-        <item x="11"/>
+        <item x="15"/>
+        <item x="16"/>
         <item x="12"/>
         <item x="13"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="30">
-        <item x="7"/>
-        <item x="16"/>
-        <item x="25"/>
-        <item x="21"/>
-        <item x="9"/>
-        <item x="5"/>
-        <item x="26"/>
-        <item x="24"/>
-        <item x="28"/>
-        <item x="3"/>
-        <item x="15"/>
-        <item x="18"/>
-        <item x="2"/>
-        <item x="14"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="13"/>
-        <item x="20"/>
-        <item x="0"/>
-        <item x="10"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="22"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="4"/>
-        <item x="19"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -13281,7 +13818,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item h="1" x="1"/>
         <item x="0"/>
@@ -13291,31 +13828,84 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
   </rowItems>
   <colItems count="1">
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Average of Sales Completion Rate" fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
+    <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="1">
-    <format dxfId="5">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
+  <chartFormats count="4">
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="12" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Month" sourceName="Month">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Month" xr10:uid="{00000000-0013-0000-FFFF-FFFF01000000}" sourceName="Month">
   <pivotTables>
     <pivotTable tabId="2" name="PivotTable1"/>
     <pivotTable tabId="2" name="PivotTable13"/>
@@ -13355,7 +13945,7 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="Slicer_Quarter" sourceName="Quarter">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Quarter" xr10:uid="{00000000-0013-0000-FFFF-FFFF02000000}" sourceName="Quarter">
   <pivotTables>
     <pivotTable tabId="2" name="PivotTable1"/>
     <pivotTable tabId="2" name="PivotTable13"/>
@@ -13387,32 +13977,32 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <slicer name="Month" cache="Slicer_Month" caption="Month" style="SlicerStyleOther1" rowHeight="241300"/>
-  <slicer name="Quarter" cache="Slicer_Quarter" caption="Quarter" style="SlicerStyleOther1" rowHeight="241300"/>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Month" xr10:uid="{00000000-0014-0000-FFFF-FFFF01000000}" cache="Slicer_Month" caption="Month" style="SlicerStyleOther1" rowHeight="241300"/>
+  <slicer name="Quarter" xr10:uid="{00000000-0014-0000-FFFF-FFFF02000000}" cache="Slicer_Quarter" caption="Quarter" style="SlicerStyleOther1" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:N64" totalsRowShown="0">
-  <autoFilter ref="A1:N64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N64" totalsRowShown="0">
+  <autoFilter ref="A1:N64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Date" dataDxfId="15"/>
-    <tableColumn id="2" name="Region"/>
-    <tableColumn id="3" name="Sales" dataCellStyle="Comma"/>
-    <tableColumn id="4" name="Profit" dataCellStyle="Comma"/>
-    <tableColumn id="5" name="Target Sales" dataCellStyle="Comma"/>
-    <tableColumn id="6" name="No of Customers"/>
-    <tableColumn id="7" name="Sales Completion Rate"/>
-    <tableColumn id="8" name="Profit Completion Rate"/>
-    <tableColumn id="9" name="Customer Completion Rate"/>
-    <tableColumn id="10" name="Country"/>
-    <tableColumn id="11" name="Customer Satisfaction"/>
-    <tableColumn id="12" name="Score"/>
-    <tableColumn id="13" name="Month" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Region"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Sales" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Profit" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Target Sales" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="No of Customers"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Sales Completion Rate"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Profit Completion Rate"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Customer Completion Rate"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Country"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Customer Satisfaction"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Score"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Month" dataDxfId="1">
       <calculatedColumnFormula>TEXT(Table1[[#This Row],[Date]], "mmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="Quarter" dataDxfId="13">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Quarter" dataDxfId="0">
       <calculatedColumnFormula>"Q"&amp;ROUNDUP(MONTH(Table1[[#This Row],[Date]])/3,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13736,30 +14326,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:O51"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="35.625" customWidth="1"/>
-    <col min="2" max="2" width="12.375" customWidth="1"/>
-    <col min="3" max="3" width="13.125" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="13.125" customWidth="1"/>
-    <col min="6" max="6" width="12.375" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="9" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.125" customWidth="1"/>
-    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="2.375" customWidth="1"/>
-    <col min="14" max="14" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.375" customWidth="1"/>
-    <col min="16" max="16" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.59765625" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" customWidth="1"/>
+    <col min="3" max="3" width="13.09765625" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="13.09765625" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" customWidth="1"/>
+    <col min="7" max="7" width="13.09765625" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" customWidth="1"/>
+    <col min="9" max="9" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.09765625" customWidth="1"/>
+    <col min="11" max="11" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="2.3984375" customWidth="1"/>
+    <col min="14" max="14" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.3984375" customWidth="1"/>
+    <col min="16" max="16" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="15">
+    <row r="2" spans="1:15">
       <c r="A2" s="7" t="s">
         <v>38</v>
       </c>
@@ -14474,16 +15064,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A10:D15"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="31.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="31.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="10" spans="1:4" ht="15">
+    <row r="10" spans="1:4">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -14518,7 +15108,7 @@
       </c>
       <c r="D12" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="15">
+    <row r="15" spans="1:4">
       <c r="A15" s="6" t="s">
         <v>47</v>
       </c>
@@ -14529,20 +15119,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N64"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="13.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="13.09765625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="16.59765625" customWidth="1"/>
     <col min="7" max="7" width="21.5" customWidth="1"/>
-    <col min="8" max="8" width="21.125" customWidth="1"/>
+    <col min="8" max="8" width="21.09765625" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="9.125" customWidth="1"/>
-    <col min="11" max="11" width="20.875" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" customWidth="1"/>
+    <col min="11" max="11" width="20.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -17496,10 +18086,10 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="Y27"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="27" spans="25:25">
       <c r="Y27" s="1" t="str">
